--- a/tame_output/ON/bt/strategyON_20230803.xlsx
+++ b/tame_output/ON/bt/strategyON_20230803.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.9%</t>
+          <t>456.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>104.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.7%</t>
+          <t>-158.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.5%</t>
+          <t>141.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>135.9%</t>
+          <t>136.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1677"/>
+  <dimension ref="A1:G1678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40081,7 +40081,7 @@
         <v>45139</v>
       </c>
       <c r="B1677" t="n">
-        <v>2.89656247465363</v>
+        <v>2.893090653419651</v>
       </c>
       <c r="C1677" t="n">
         <v>3.009114324181228</v>
@@ -40097,6 +40097,29 @@
       </c>
       <c r="G1677" t="n">
         <v>4.296729532207901</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="2" t="n">
+        <v>45140</v>
+      </c>
+      <c r="B1678" t="n">
+        <v>2.87719753980562</v>
+      </c>
+      <c r="C1678" t="n">
+        <v>3.014046102192081</v>
+      </c>
+      <c r="D1678" t="n">
+        <v>1.528923481445531</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>3.625259070456547</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>2.152424203482064</v>
+      </c>
+      <c r="G1678" t="n">
+        <v>4.305500624281321</v>
       </c>
     </row>
   </sheetData>
